--- a/src/main/resources/Trades.xlsx
+++ b/src/main/resources/Trades.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiephuynh/Documents/apps/formater/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299D9C28-0820-DB45-A707-E0E2CF93BCDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA41EE9-24A9-EF41-A14E-A2E82CF85FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1180" yWindow="500" windowWidth="14000" windowHeight="15940" xr2:uid="{AAE9CA0E-4B36-2642-B2A9-913704820BE0}"/>
+    <workbookView xWindow="1180" yWindow="500" windowWidth="14000" windowHeight="15940" activeTab="1" xr2:uid="{AAE9CA0E-4B36-2642-B2A9-913704820BE0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,35 +40,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="40">
   <si>
     <t>Symbol</t>
   </si>
   <si>
-    <t>SGD</t>
-  </si>
-  <si>
-    <t>STI</t>
-  </si>
-  <si>
-    <t>GRYP</t>
-  </si>
-  <si>
-    <t>PIK</t>
-  </si>
-  <si>
-    <t>RVSN</t>
-  </si>
-  <si>
-    <t>UMAC</t>
-  </si>
-  <si>
-    <t>DUO</t>
-  </si>
-  <si>
-    <t>TCBP</t>
-  </si>
-  <si>
     <t>Time</t>
   </si>
   <si>
@@ -84,37 +60,106 @@
     <t>Exit Price</t>
   </si>
   <si>
-    <t>09:11:24</t>
-  </si>
-  <si>
-    <t>03/11/24</t>
-  </si>
-  <si>
-    <t>12:46:43</t>
-  </si>
-  <si>
-    <t>07:42:03</t>
-  </si>
-  <si>
-    <t>10:42:21</t>
-  </si>
-  <si>
-    <t>13:01:37</t>
-  </si>
-  <si>
-    <t>09:35:59</t>
-  </si>
-  <si>
-    <t>07:30:09</t>
-  </si>
-  <si>
-    <t>08:18:50</t>
-  </si>
-  <si>
-    <t>09:19:04</t>
-  </si>
-  <si>
-    <t>08:54:29</t>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Quantity2</t>
+  </si>
+  <si>
+    <t>Exec Time</t>
+  </si>
+  <si>
+    <t>Spread</t>
+  </si>
+  <si>
+    <t>Side</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>Pos Effect</t>
+  </si>
+  <si>
+    <t>Exp</t>
+  </si>
+  <si>
+    <t>Strike</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Net Price</t>
+  </si>
+  <si>
+    <t>Order Type</t>
+  </si>
+  <si>
+    <t>STOCK</t>
+  </si>
+  <si>
+    <t>SELL</t>
+  </si>
+  <si>
+    <t>TO CLOSE</t>
+  </si>
+  <si>
+    <t>WHLR</t>
+  </si>
+  <si>
+    <t>LMT</t>
+  </si>
+  <si>
+    <t>BUY</t>
+  </si>
+  <si>
+    <t>TO OPEN</t>
+  </si>
+  <si>
+    <t>TPET</t>
+  </si>
+  <si>
+    <t>KWE</t>
+  </si>
+  <si>
+    <t>AISP</t>
+  </si>
+  <si>
+    <t>MKT</t>
+  </si>
+  <si>
+    <t>KITT</t>
+  </si>
+  <si>
+    <t>07:06:50</t>
+  </si>
+  <si>
+    <t>06/11/24</t>
+  </si>
+  <si>
+    <t>10:37:35</t>
+  </si>
+  <si>
+    <t>10:07:57</t>
+  </si>
+  <si>
+    <t>09:48:18</t>
+  </si>
+  <si>
+    <t>11:35:39</t>
+  </si>
+  <si>
+    <t>07:24:44</t>
+  </si>
+  <si>
+    <t>07:36:40</t>
+  </si>
+  <si>
+    <t>08:23:08</t>
+  </si>
+  <si>
+    <t>15:22:51</t>
   </si>
 </sst>
 </file>
@@ -490,246 +535,1958 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2CEB716-14AC-3A42-B984-283B8796299A}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.1640625" style="1" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="18.1640625" collapsed="false"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>45454.64166666667</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2">
+        <v>-100</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2">
+        <v>2.59</v>
+      </c>
+      <c r="K2">
+        <v>2.59</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>45454.640868055554</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3">
+        <v>2.68</v>
+      </c>
+      <c r="K3">
+        <v>2.68</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>45454.483356481483</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>-1000</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4">
+        <v>0.38379999999999997</v>
+      </c>
+      <c r="K4">
+        <v>0.38379999999999997</v>
+      </c>
+      <c r="L4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>45454.483090277776</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5">
+        <v>1000</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5">
+        <v>0.37290000000000001</v>
+      </c>
+      <c r="K5">
+        <v>0.37290000000000001</v>
+      </c>
+      <c r="L5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>45454.447268518517</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6">
+        <v>-300</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6">
+        <v>1.0306999999999999</v>
+      </c>
+      <c r="K6">
+        <v>1.0306999999999999</v>
+      </c>
+      <c r="L6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>45454.442766203705</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>300</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>45454.423900462964</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8">
+        <v>-100</v>
+      </c>
+      <c r="E8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8">
+        <v>4.2949999999999999</v>
+      </c>
+      <c r="K8">
+        <v>4.2949999999999999</v>
+      </c>
+      <c r="L8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>45454.4221875</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9">
+        <v>50</v>
+      </c>
+      <c r="E9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9">
+        <v>4.4397000000000002</v>
+      </c>
+      <c r="K9">
+        <v>4.4396000000000004</v>
+      </c>
+      <c r="L9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>45454.421168981484</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10">
+        <v>4.415</v>
+      </c>
+      <c r="K10">
+        <v>4.4148800000000001</v>
+      </c>
+      <c r="L10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>45454.421168981484</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11">
+        <v>7</v>
+      </c>
+      <c r="E11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11">
+        <v>4.415</v>
+      </c>
+      <c r="K11">
+        <v>4.4142900000000003</v>
+      </c>
+      <c r="L11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>45454.412372685183</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12">
+        <v>-700</v>
+      </c>
+      <c r="E12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12">
+        <v>0.40039999999999998</v>
+      </c>
+      <c r="K12">
+        <v>0.40039999999999998</v>
+      </c>
+      <c r="L12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>45454.411064814813</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13">
+        <v>-300</v>
+      </c>
+      <c r="E13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13">
+        <v>0.43049999999999999</v>
+      </c>
+      <c r="K13">
+        <v>0.43049999999999999</v>
+      </c>
+      <c r="L13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>45454.40996527778</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14">
+        <v>-300</v>
+      </c>
+      <c r="E14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14">
+        <v>0.42470000000000002</v>
+      </c>
+      <c r="K14">
+        <v>0.42470000000000002</v>
+      </c>
+      <c r="L14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>45454.40996527778</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15">
+        <v>-300</v>
+      </c>
+      <c r="E15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15">
+        <v>0.42470000000000002</v>
+      </c>
+      <c r="K15">
+        <v>0.42470000000000002</v>
+      </c>
+      <c r="L15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>45454.40996527778</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16">
+        <v>-400</v>
+      </c>
+      <c r="E16" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16">
+        <v>0.42470000000000002</v>
+      </c>
+      <c r="K16">
+        <v>0.42470000000000002</v>
+      </c>
+      <c r="L16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>45454.408541666664</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17">
+        <v>1000</v>
+      </c>
+      <c r="E17" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17">
+        <v>0.39710000000000001</v>
+      </c>
+      <c r="K17">
+        <v>0.39710000000000001</v>
+      </c>
+      <c r="L17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>45454.407766203702</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18">
+        <v>1000</v>
+      </c>
+      <c r="E18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="K18">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="L18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>45454.351273148146</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19">
+        <v>-1000</v>
+      </c>
+      <c r="E19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19">
+        <v>0.35199999999999998</v>
+      </c>
+      <c r="K19">
+        <v>0.35199999999999998</v>
+      </c>
+      <c r="L19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>45454.350972222222</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20">
+        <v>-100</v>
+      </c>
+      <c r="E20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" t="s">
+        <v>29</v>
+      </c>
+      <c r="I20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20">
+        <v>0.34639999999999999</v>
+      </c>
+      <c r="K20">
+        <v>0.34639999999999999</v>
+      </c>
+      <c r="L20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>45454.350972222222</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21">
+        <v>-250</v>
+      </c>
+      <c r="E21" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I21" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21">
+        <v>0.3463</v>
+      </c>
+      <c r="K21">
+        <v>0.34632000000000002</v>
+      </c>
+      <c r="L21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>45454.350972222222</v>
+      </c>
+      <c r="B22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22">
+        <v>-250</v>
+      </c>
+      <c r="E22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22">
+        <v>0.3463</v>
+      </c>
+      <c r="K22">
+        <v>0.34632000000000002</v>
+      </c>
+      <c r="L22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>45454.350972222222</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23">
+        <v>-50</v>
+      </c>
+      <c r="E23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" t="s">
+        <v>29</v>
+      </c>
+      <c r="I23" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23">
+        <v>0.34639999999999999</v>
+      </c>
+      <c r="K23">
+        <v>0.34639999999999999</v>
+      </c>
+      <c r="L23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>45454.350972222222</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24">
+        <v>-100</v>
+      </c>
+      <c r="E24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" t="s">
+        <v>29</v>
+      </c>
+      <c r="I24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24">
+        <v>0.34639999999999999</v>
+      </c>
+      <c r="K24">
+        <v>0.34639999999999999</v>
+      </c>
+      <c r="L24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>45454.350972222222</v>
+      </c>
+      <c r="B25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25">
+        <v>-250</v>
+      </c>
+      <c r="E25" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" t="s">
+        <v>29</v>
+      </c>
+      <c r="I25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J25">
+        <v>0.34639999999999999</v>
+      </c>
+      <c r="K25">
+        <v>0.34639999999999999</v>
+      </c>
+      <c r="L25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>45454.350069444445</v>
+      </c>
+      <c r="B26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26">
+        <v>-1000</v>
+      </c>
+      <c r="E26" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J26">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="K26">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="L26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>45454.350034722222</v>
+      </c>
+      <c r="B27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27">
+        <v>-1000</v>
+      </c>
+      <c r="E27" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" t="s">
+        <v>29</v>
+      </c>
+      <c r="I27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27">
+        <v>0.3453</v>
+      </c>
+      <c r="K27">
+        <v>0.3453</v>
+      </c>
+      <c r="L27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>45454.349398148152</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28">
+        <v>1000</v>
+      </c>
+      <c r="E28" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" t="s">
+        <v>29</v>
+      </c>
+      <c r="I28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28">
+        <v>0.33679999999999999</v>
+      </c>
+      <c r="K28">
+        <v>0.33679999999999999</v>
+      </c>
+      <c r="L28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>45454.349386574075</v>
+      </c>
+      <c r="B29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29">
+        <v>800</v>
+      </c>
+      <c r="E29" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J29">
+        <v>0.33700000000000002</v>
+      </c>
+      <c r="K29">
+        <v>0.33700000000000002</v>
+      </c>
+      <c r="L29" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>45454.349386574075</v>
+      </c>
+      <c r="B30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30">
+        <v>200</v>
+      </c>
+      <c r="E30" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" t="s">
+        <v>29</v>
+      </c>
+      <c r="I30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J30">
+        <v>0.33700000000000002</v>
+      </c>
+      <c r="K30">
+        <v>0.33700000000000002</v>
+      </c>
+      <c r="L30" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>45454.349386574075</v>
+      </c>
+      <c r="B31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31">
+        <v>1000</v>
+      </c>
+      <c r="E31" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" t="s">
+        <v>29</v>
+      </c>
+      <c r="I31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J31">
+        <v>0.33689999999999998</v>
+      </c>
+      <c r="K31">
+        <v>0.33689999999999998</v>
+      </c>
+      <c r="L31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>45454.345625000002</v>
+      </c>
+      <c r="B32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32">
+        <v>25</v>
+      </c>
+      <c r="E32" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" t="s">
+        <v>29</v>
+      </c>
+      <c r="I32" t="s">
+        <v>18</v>
+      </c>
+      <c r="J32">
+        <v>0.3286</v>
+      </c>
+      <c r="K32">
+        <v>0.32879999999999998</v>
+      </c>
+      <c r="L32" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>45454.345613425925</v>
+      </c>
+      <c r="B33" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33">
+        <v>100</v>
+      </c>
+      <c r="E33" t="s">
+        <v>24</v>
+      </c>
+      <c r="F33" t="s">
+        <v>29</v>
+      </c>
+      <c r="I33" t="s">
+        <v>18</v>
+      </c>
+      <c r="J33">
+        <v>0.3286</v>
+      </c>
+      <c r="K33">
+        <v>0.3286</v>
+      </c>
+      <c r="L33" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>45454.345613425925</v>
+      </c>
+      <c r="B34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34">
+        <v>577</v>
+      </c>
+      <c r="E34" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" t="s">
+        <v>29</v>
+      </c>
+      <c r="I34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J34">
+        <v>0.3286</v>
+      </c>
+      <c r="K34">
+        <v>0.3286</v>
+      </c>
+      <c r="L34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>45454.345601851855</v>
+      </c>
+      <c r="B35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35">
+        <v>155</v>
+      </c>
+      <c r="E35" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35" t="s">
+        <v>29</v>
+      </c>
+      <c r="I35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35">
+        <v>0.3286</v>
+      </c>
+      <c r="K35">
+        <v>0.32857999999999998</v>
+      </c>
+      <c r="L35" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>45454.345601851855</v>
+      </c>
+      <c r="B36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36">
+        <v>143</v>
+      </c>
+      <c r="E36" t="s">
+        <v>24</v>
+      </c>
+      <c r="F36" t="s">
+        <v>29</v>
+      </c>
+      <c r="I36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36">
+        <v>0.3286</v>
+      </c>
+      <c r="K36">
+        <v>0.3286</v>
+      </c>
+      <c r="L36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>45454.321250000001</v>
+      </c>
+      <c r="B37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37">
+        <v>-999</v>
+      </c>
+      <c r="E37" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" t="s">
+        <v>29</v>
+      </c>
+      <c r="I37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37">
+        <v>0.38179999999999997</v>
+      </c>
+      <c r="K37">
+        <v>0.38179999999999997</v>
+      </c>
+      <c r="L37" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>45454.321250000001</v>
+      </c>
+      <c r="B38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38">
+        <v>-1</v>
+      </c>
+      <c r="E38" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" t="s">
+        <v>29</v>
+      </c>
+      <c r="I38" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38">
+        <v>0.38179999999999997</v>
+      </c>
+      <c r="K38">
+        <v>0.38</v>
+      </c>
+      <c r="L38" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>45454.320798611108</v>
+      </c>
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39">
+        <v>-1000</v>
+      </c>
+      <c r="E39" t="s">
+        <v>20</v>
+      </c>
+      <c r="F39" t="s">
+        <v>29</v>
+      </c>
+      <c r="I39" t="s">
+        <v>18</v>
+      </c>
+      <c r="J39">
+        <v>0.38069999999999998</v>
+      </c>
+      <c r="K39">
+        <v>0.38069999999999998</v>
+      </c>
+      <c r="L39" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>45454.317129629628</v>
+      </c>
+      <c r="B40" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40">
+        <v>300</v>
+      </c>
+      <c r="E40" t="s">
+        <v>24</v>
+      </c>
+      <c r="F40" t="s">
+        <v>29</v>
+      </c>
+      <c r="I40" t="s">
+        <v>18</v>
+      </c>
+      <c r="J40">
+        <v>0.37830000000000003</v>
+      </c>
+      <c r="K40">
+        <v>0.37830000000000003</v>
+      </c>
+      <c r="L40" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>45454.317129629628</v>
+      </c>
+      <c r="B41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41">
+        <v>700</v>
+      </c>
+      <c r="E41" t="s">
+        <v>24</v>
+      </c>
+      <c r="F41" t="s">
+        <v>29</v>
+      </c>
+      <c r="I41" t="s">
+        <v>18</v>
+      </c>
+      <c r="J41">
+        <v>0.37830000000000003</v>
+      </c>
+      <c r="K41">
+        <v>0.37830000000000003</v>
+      </c>
+      <c r="L41" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>45454.315717592595</v>
+      </c>
+      <c r="B42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42">
+        <v>1000</v>
+      </c>
+      <c r="E42" t="s">
+        <v>24</v>
+      </c>
+      <c r="F42" t="s">
+        <v>29</v>
+      </c>
+      <c r="I42" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42">
+        <v>0.38150000000000001</v>
+      </c>
+      <c r="K42">
+        <v>0.38150000000000001</v>
+      </c>
+      <c r="L42" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>45454.310763888891</v>
+      </c>
+      <c r="B43" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43">
+        <v>-1000</v>
+      </c>
+      <c r="E43" t="s">
+        <v>20</v>
+      </c>
+      <c r="F43" t="s">
+        <v>29</v>
+      </c>
+      <c r="I43" t="s">
+        <v>18</v>
+      </c>
+      <c r="J43">
+        <v>0.40989999999999999</v>
+      </c>
+      <c r="K43">
+        <v>0.40989999999999999</v>
+      </c>
+      <c r="L43" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>45454.309583333335</v>
+      </c>
+      <c r="B44" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44">
+        <v>-1000</v>
+      </c>
+      <c r="E44" t="s">
+        <v>20</v>
+      </c>
+      <c r="F44" t="s">
+        <v>29</v>
+      </c>
+      <c r="I44" t="s">
+        <v>18</v>
+      </c>
+      <c r="J44">
+        <v>0.42549999999999999</v>
+      </c>
+      <c r="K44">
+        <v>0.42549999999999999</v>
+      </c>
+      <c r="L44" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>45454.308842592596</v>
+      </c>
+      <c r="B45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" t="s">
+        <v>23</v>
+      </c>
+      <c r="D45">
+        <v>1000</v>
+      </c>
+      <c r="E45" t="s">
+        <v>24</v>
+      </c>
+      <c r="F45" t="s">
+        <v>29</v>
+      </c>
+      <c r="I45" t="s">
+        <v>18</v>
+      </c>
+      <c r="J45">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="K45">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="L45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>45454.308842592596</v>
+      </c>
+      <c r="B46" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" t="s">
+        <v>23</v>
+      </c>
+      <c r="D46">
+        <v>1000</v>
+      </c>
+      <c r="E46" t="s">
+        <v>24</v>
+      </c>
+      <c r="F46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I46" t="s">
+        <v>18</v>
+      </c>
+      <c r="J46">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="K46">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="L46" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>45454.299571759257</v>
+      </c>
+      <c r="B47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47">
+        <v>-10</v>
+      </c>
+      <c r="E47" t="s">
+        <v>20</v>
+      </c>
+      <c r="F47" t="s">
+        <v>26</v>
+      </c>
+      <c r="I47" t="s">
+        <v>18</v>
+      </c>
+      <c r="J47">
+        <v>0.91759999999999997</v>
+      </c>
+      <c r="K47">
+        <v>0.91800000000000004</v>
+      </c>
+      <c r="L47" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>45454.29896990741</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48">
+        <v>-75</v>
+      </c>
+      <c r="E48" t="s">
+        <v>20</v>
+      </c>
+      <c r="F48" t="s">
+        <v>26</v>
+      </c>
+      <c r="I48" t="s">
+        <v>18</v>
+      </c>
+      <c r="J48">
+        <v>0.91359999999999997</v>
+      </c>
+      <c r="K48">
+        <v>0.91359999999999997</v>
+      </c>
+      <c r="L48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>45454.298611111109</v>
+      </c>
+      <c r="B49" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49">
+        <v>-200</v>
+      </c>
+      <c r="E49" t="s">
+        <v>20</v>
+      </c>
+      <c r="F49" t="s">
+        <v>26</v>
+      </c>
+      <c r="I49" t="s">
+        <v>18</v>
+      </c>
+      <c r="J49">
+        <v>0.91359999999999997</v>
+      </c>
+      <c r="K49">
+        <v>0.91359999999999997</v>
+      </c>
+      <c r="L49" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>45454.298460648148</v>
+      </c>
+      <c r="B50" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50">
+        <v>-215</v>
+      </c>
+      <c r="E50" t="s">
+        <v>20</v>
+      </c>
+      <c r="F50" t="s">
+        <v>26</v>
+      </c>
+      <c r="I50" t="s">
+        <v>18</v>
+      </c>
+      <c r="J50">
+        <v>0.91359999999999997</v>
+      </c>
+      <c r="K50">
+        <v>0.91357999999999995</v>
+      </c>
+      <c r="L50" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>45454.297361111108</v>
+      </c>
+      <c r="B51" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51">
+        <v>-490</v>
+      </c>
+      <c r="E51" t="s">
+        <v>20</v>
+      </c>
+      <c r="F51" t="s">
+        <v>26</v>
+      </c>
+      <c r="I51" t="s">
+        <v>18</v>
+      </c>
+      <c r="J51">
+        <v>0.91359999999999997</v>
+      </c>
+      <c r="K51">
+        <v>0.91359000000000001</v>
+      </c>
+      <c r="L51" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>45454.296412037038</v>
+      </c>
+      <c r="B52" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" t="s">
+        <v>23</v>
+      </c>
+      <c r="D52">
+        <v>990</v>
+      </c>
+      <c r="E52" t="s">
+        <v>24</v>
+      </c>
+      <c r="F52" t="s">
+        <v>26</v>
+      </c>
+      <c r="I52" t="s">
+        <v>18</v>
+      </c>
+      <c r="J52">
+        <v>0.88280000000000003</v>
+      </c>
+      <c r="K52">
+        <v>0.88280000000000003</v>
+      </c>
+      <c r="L52" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="6.62109375" collapsed="false"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="8.56640625" collapsed="false"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="6.0" collapsed="false"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="4.1640625" collapsed="false"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="12.33203125" collapsed="false"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="9.27734375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>100</v>
-      </c>
-      <c r="E2">
-        <v>1.44</v>
-      </c>
-      <c r="F2">
-        <v>1.36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" t="n">
+        <v>990.0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.8828</v>
+      </c>
+      <c r="K2" t="n">
+        <v>990.0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.9136351515151515</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>70</v>
-      </c>
-      <c r="E3">
-        <v>2.0214285714285714</v>
-      </c>
-      <c r="F3">
-        <v>1.8701399999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.0307</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>100</v>
-      </c>
-      <c r="E4">
-        <v>8.9499999999999993</v>
-      </c>
-      <c r="F4">
-        <v>9.4084000000000003</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.4271987</v>
+      </c>
+      <c r="K4" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4.295</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>50</v>
-      </c>
-      <c r="E5">
-        <v>6.86</v>
-      </c>
-      <c r="F5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.39605</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.417065</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="F6">
-        <v>2.4500000000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.3838</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>100</v>
-      </c>
-      <c r="E7">
-        <v>3.23</v>
-      </c>
-      <c r="F7">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.4177</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.37989999999999996</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.38124909999999995</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4000.0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.334825475</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4000.0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.347165</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" t="s">
         <v>21</v>
       </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8">
-        <v>300</v>
-      </c>
-      <c r="E8">
-        <v>1.58</v>
-      </c>
-      <c r="F8">
-        <v>1.6767666666666665</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9">
-        <v>100</v>
-      </c>
-      <c r="E9">
-        <v>1.7</v>
-      </c>
-      <c r="F9">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10">
-        <v>100</v>
-      </c>
-      <c r="E10">
-        <v>5.3</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11">
-        <v>100</v>
-      </c>
-      <c r="E11">
-        <v>1.35</v>
-      </c>
-      <c r="F11">
-        <v>1.27</v>
+      <c r="H10" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K10" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.59</v>
       </c>
     </row>
   </sheetData>
